--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84483124</v>
+        <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,13 +712,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552011.6299289876</v>
+        <v>552171</v>
       </c>
       <c r="R2" t="n">
-        <v>6681990.458107198</v>
+        <v>6681885</v>
       </c>
       <c r="S2" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84483087</v>
+        <v>84483124</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,17 +817,17 @@
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nötterödingen, Dlr</t>
+          <t>Hedemora, Hedemora kommun, Svealand, Västkustvägen, Västkusten, Svedjan, Da, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552062.8888027685</v>
+        <v>552012</v>
       </c>
       <c r="R3" t="n">
-        <v>6681950.996805721</v>
+        <v>6681990</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,6 +890,347 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>84488149</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nötterödningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>551911</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6681937</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>84488095</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nötterödningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>551911</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6681937</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>84483087</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nötterödingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552063</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6681951</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84483082</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84483124</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84488149</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84488095</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,8 +1256,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84483087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96554</v>
+        <v>96725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4031-2022 artfynd.xlsx
+++ b/artfynd/A 4031-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>84483082</v>
       </c>
       <c r="B2" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
